--- a/estructura/output/boards_columns.xlsx
+++ b/estructura/output/boards_columns.xlsx
@@ -7,15 +7,14 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="compras_pagos_3169137106" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="caja_chica_chilpancingo_7269476" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="agente_soporte_campo_7072610932" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="soporte_operativo_5914627798" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="acciones_5355817123" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="anuncios_penalizados_7019548313" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="resoluciones_6908297780" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="solicitudes_mantenimiento_26632" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Limpiezas_4460406422" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="monday_properties_main_32709608" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="monday_properties_general_40454" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="monday_properties_equipme_40453" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="monday_properties_ameniti_40454" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="monday_properties_accesor_40454" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="monday_properties_service_40455" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="monday_properties_present_40455" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="monday_properties_checkin_63114" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -421,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,7 +450,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>subitems</t>
+          <t>subelementos</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -463,204 +462,1008 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>long_text</t>
+          <t>status</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Motivo</t>
+          <t>🌐 Estado</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>conectar_tableros85</t>
+          <t>reflejo_mkmeqnsy</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Proveedores</t>
+          <t>Reflejo</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>reflejo9</t>
+          <t>reflejo172</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Datos Bancarios</t>
+          <t>📋 Notas importantes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>conectar_tableros8</t>
+          <t>enlace5</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>🔗 Check-in Guide Link</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>file</t>
+          <t>enlace</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Archivos</t>
+          <t>🔗 Link Airbnb</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>label</t>
+          <t>personas0</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tipo de compra</t>
+          <t>🫧 Personal de limpieza</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>dup__of_costo_aproximado</t>
+          <t>multiple_person__1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Costo final</t>
+          <t>🔧 Personal de mantenimiento</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>files</t>
+          <t>multiple_person3__1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>🗳️ Personal de Soporte</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>m_todo_de_pago</t>
+          <t>personas__1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Método de Pago</t>
+          <t>🔍 Supervisor</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>f_rmula</t>
+          <t>personas6__1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Concepto de pago</t>
+          <t>👁️ Visibilidad</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>archivo</t>
+          <t>dup__of____visibilidad_mkm7s2wb</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Comprobante de pago</t>
+          <t>👩🏼‍✈️Vigilancia / Administración</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>numeric1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>👩🏼‍✈️ Vigilancia User ID</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>reflejo70</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fecha de pago</t>
+          <t>💁 Cliente</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>creation_log</t>
+          <t>reflejo68</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Creado</t>
+          <t>🗺️ Dirección</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>pulse_updated</t>
+          <t>men__desplegable8</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Última actualización</t>
+          <t>📲 Método de registro</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>link_to_agenda_mike</t>
+          <t>reflejo9</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>link to Agenda Mike</t>
+          <t>🔑 Acceso depto.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>men__desplegable__1</t>
+          <t>reflejo54</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tarjeta</t>
+          <t>🔑 Acceso edificio</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>reflejo130</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>🗑️ Ubicación Basurero</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>reflejo058</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>📕 Reglamentos del edificio</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>reflejo94</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>🗑️ Basurero</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>reflejo39</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>🚘 Estacionamiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>reflejo23</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>🚘 Estacionamiento Foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>reflejo06</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>🛜 WiFi</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>reflejo03</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>🛜 Contraseña</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>reflejo08</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>🛜 Velocidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>reflejo102</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>🛜  Compañía</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>conectar_tableros32</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>🏢 Información general</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>conectar_tableros1</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>🏢 Equipos y dispositivos</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>conectar_tableros25</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>🏢 Amenidades</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>conectar_tableros34</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>🏢 Blancos y accesorios</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>conectar_tableros29</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>🏢 Servicios</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>conectar_tableros4</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>🏢 Estándares de Presentación</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>conectar_tableros__1</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>🏢 Check-in guide</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>board_relation__1</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>🏢 Grupos de WhatsApp</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>link_to_avisos__1</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>📰  Avisos</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>board_relation8</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>💁 Propiedad de Clientes</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>dup__of_paquete6</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>📄Modalidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>cuenta_airbnb__1</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>🚫 Cuenta Airbnb</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>dup__of_modalidad__1</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>🌐 Cuenta Airbnb</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>reflejo49</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>👩🏼‍✈️Administrador</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>reflejo0</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>👩🏼‍✈️ Contacto Administrador</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>estado_13</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>✅ Anuncio en Airbnb</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>color</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>✅ Descuentos</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>dup__of___descuentos_Mjj4RSaV</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>✅ Clau = Anfitriona principal</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>color_mkkt3gem</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>✅ Rodrigo co-host</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>color3</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>✅ Mensajes Hospitable</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>reflejo4</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>✅ Equipos y dispositivos</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>reflejo17</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>✅ Estándares de presentación</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>reflejo5</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>✅ Información General</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>reflejo2</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>✅ Servicios</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>reflejo_19</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>✅ Blancos y Accesorios</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>reflejo36</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>✅ Amenidades</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>texto2</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>📋 Nombre Corto</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>texto86</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>📋 Nombre en Airbnb</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>texto02</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>📋 (En) Nombre Airbnb</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>id_propiedad</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>📋 Airbnb ID propiedad</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>mike___hosp_id</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>📋 Hosp ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>__hosp_uuid_Mjj5oqhN</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>📋 Hosp UUID</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>texto09</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>📋 CalendarID</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>f_rmula3</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>🌐 Tabulador Limpieza</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>n_meros29</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>📋 Tarifa Limpieza Huépsed</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>n_meros2</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>💵 Pago Personal de Limpieza</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>n_meros</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>🌐 Tabulador $ por noche</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>n_meros90</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>📋 Precio por noche real</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>🌐 Tabulador Fin de semana</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>numeric2</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>📋 Precio por fin de semana real</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>men__desplegable7</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>🗺️ Zona</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>ciudad__1</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>🌎 Ciudad</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>label__1</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>🏷️ Label</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>estado_1__1</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>📷 Fotos Profesionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>board_relation5</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>🔍 Supervisión de limpiezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>reflejo51</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>🗓️ Fecha última supervisión</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>lookup9</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>🔍 Superv. últimos 3 meses</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>monday_doc_v2__1</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>monday Doc v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>reflejo_Mjj2eJgI</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>⚙️ No. Recámaras</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>board_relation_mkmv5m8g</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>⚠️ Penalizaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>reflejo_1_mkmvhsv9</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>⚠️ Penalización</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>dup__of____penalizaci_n_mkmv2e47</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>⚠️ Fecha Penalización</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>registro_de_creaci_n_mkmbre94</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Registro de creación</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>_ltima_actualizaci_n</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Última actualización</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>casilla_de_verificaci_n_mkmwkqrg</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>En proceso de Duplicar</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>link_to___calendario_mkmxvdet</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>link to 🏢 Calendario</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>id_de_elemento_mkn314vp</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>ID de elemento</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>board_relation_mkpvk69p</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>link to Reportes Inspecciones</t>
         </is>
       </c>
     </row>
@@ -675,7 +1478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -717,120 +1520,924 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>texto16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fecha</t>
+          <t>Número de huéspedes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>horas_extras5__1</t>
+          <t>men__desplegable</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$ Movimiento</t>
+          <t>Tipo de propiedad</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>label__1</t>
+          <t>men__desplegable6</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tipo</t>
+          <t>Piso</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>horas_extras__1</t>
+          <t>estado</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Detalle</t>
+          <t>Elevador</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>archivo__1</t>
+          <t>dup__of_piso</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Documento</t>
+          <t>Total de pisos en el edificio</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>personas__1</t>
+          <t>texto47</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Personas</t>
+          <t>Administración: Nombre y Contacto</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>f_rmula__1</t>
+          <t>archivo3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Saldo</t>
+          <t>Reglamentos del edificio</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>estado__1</t>
+          <t>reflejo</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Método de registro</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>texto1__1</t>
+          <t>texto10</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Observaciones</t>
+          <t>Detalles de registro</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>f_rmula0__1</t>
+          <t>estado38</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pago horas extra</t>
+          <t>Vigilancia / Recepción</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>texto5</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Nombres y Contacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>texto259</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Horarios</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>texto74</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Acceso al edificio</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>texto69</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Acceso al departamento</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>text_mkq731zq</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Copia de llaves soporte</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>men__desplegable1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dispositivo de entrada</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>texto0</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ubicación Basurero</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>archivo</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Foto Basurero</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>n_meros</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Número de baños</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>dup__of_rec_mara_1</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Balcón / Terraza privada</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>estado_13</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Recámara 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>camas__r1_</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Camas (R1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>texto28</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Tamaño (R1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>estado1</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Baño privado (R1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>color</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Recámara 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>camas__r2_</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Camas (R2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>texto24</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Tamaño (R2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>estado9</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Baño privado (R2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>color4</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Recámara 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>camas__r3_</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Camas (R3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>texto7</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Tamaño (R3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>estado11</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Baño privado</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>color0</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>+ Recámaras</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t># recámaras adicionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>numeric5</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Número de camas adicionales +R</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>texto09</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Tamaño de camas adicionales +R</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>texto44</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Baño privado +R</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>estado3</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>🛋️ Sofacama(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>texto3</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>🛋️ Número y ubicación: Sofacama(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>texto60</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>🛋️ Tamaño y capacidad de huéspedes: Sofacama(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>texto_largo</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>🛋️ Instrucciones sábanas y almohadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>archivo6</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>🛋️ Foto: Sofacama(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>texto_largo3</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Notas importantes</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>long_text</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Instrucciones almacén interno</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>archivo35</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Foto del almacén del limpieza</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>color5</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Escritorio de trabajo</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>estado20</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Estacionamiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>texto_largo31</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Instrucciones, ubicación y/o notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>archivo7</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>estado_1</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Persianas opacas en cuartos</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>texto36</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Notas Persianas</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>estado25</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>El edificio cuenta con cisterna o reservas de agua</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>texto_largo58</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Plan de contingencia en caso de falta de agua</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>texto_largo__1</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Condiciones ambientales</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>color46</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Mascotas</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>reflejo0</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Personal de limpieza</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>reflejo6</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Inspección Mantenimiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>estado2</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Estado Información General</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>board_relation4</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Link to Fichas - Propiedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>f_rmula</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Automático - No. de Recámaras</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Automático - No. de Camas</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>pulse_log</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Creación de registro</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>conectar_tableros7</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Link 🔧 Revisión Mantenimiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>reflejo_mkkcctfd</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>🔧 Estado</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>reflejo00</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Zona</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>board_relation</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>📝 Supervisión de limpiezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>reflejo65</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>No modificar -Supervisión últimos 3 meses</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>reflejo__1</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>reflejo7__1</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Link Estado</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>estado_1__1</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>personas_mkkay0ry</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Visibilidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>conectar_tableros_mkkc9qch</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Link 🗳️ Onboarding Operativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>reflejo_mkkccnt8</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>🗳️ Estado</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>board_relation_mkkc7vq0</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>🫧 Apertura Ama de Llaves</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>reflejo_mkkcemtk</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>🫧 Estado</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>id_de_elemento_mkmr9rw9</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>ID de elemento</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>pulse_updated_mkqa1962</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Última actualización</t>
         </is>
       </c>
     </row>
@@ -845,7 +2452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -868,14 +2475,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Nombre</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>subelementos__1</t>
+          <t>subelementos</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -887,144 +2494,624 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>estado</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fecha</t>
+          <t>TV</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>n_meros9__1</t>
+          <t>n_meros</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Horas</t>
+          <t>Cuántas?</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>horas_extras5__1</t>
+          <t>texto_1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>$ Movimiento</t>
+          <t>Marca, tamaño TV y ubicación</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>label__1</t>
+          <t>texto72</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tipo</t>
+          <t>Streaming: TV</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>horas_extras__1</t>
+          <t>archivo_1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Detalle</t>
+          <t>TV: Foto</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>archivo__1</t>
+          <t>estado1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Documento</t>
+          <t>Calentador</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>personas__1</t>
+          <t>texto97</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Personas</t>
+          <t>Número y ubicación: Calentador</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>f_rmula__1</t>
+          <t>archivo_16</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Saldo</t>
+          <t>Calentador: Fotos</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>estado__1</t>
+          <t>estado5</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Ventilador</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>texto1__1</t>
+          <t>texto91</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Observaciones</t>
+          <t>Número y ubicación: Ventilador</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>f_rmula0__1</t>
+          <t>archivo_15</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pago horas extra</t>
+          <t>Ventilador: Fotos</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>conectar_tableros__1</t>
+          <t>estado15</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Propiedades</t>
+          <t>Plancha</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>archivo84</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Foto: Plancha</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>estado3</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Secadora de pelo</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>archivo2</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Foto: Secadora de pelo</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>estado8</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Estufa</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>texto792</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Marca, número de hornillas y tipo: Estufa</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>archivo</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Foto: Estufa</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>estado54</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Refrigerador</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>texto29</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Marca y modelo: Refrigerador</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>archivo5</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Foto: Refrigerador</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>estado0</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Cafetera</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>archivo31</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Foto: Cafetera</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>estado17</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Licuadora</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>archivo96</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Foto: Licuadora</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>estado03</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Microondas</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>archivo28</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Foto: Microondas</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>estado2</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Lavadora</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>texto58</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Marca y modelo: Lavadora</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>archivo_14</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Foto: Lavadora</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>estado9</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Secadora</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>texto0</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Marca y modelo: Secadora</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>archivo27</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Foto: Secadora</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>texto4</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Boiler: Marca, modelo y tipo;</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>archivo82</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Boiler: Foto</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>text_mkqed5gj</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Boiler instrucciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>estado6</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Detector Humo/Monóxido</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>texto79</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Detector tipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>archivo7</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Foto: Detector(es)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>estado7</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Filtro de Agua</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>texto75</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Detalles: Filtro de Agua</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>archivo51</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Foto: Filtro de Agua</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>color</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Aire Acondicionado</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>archivo24</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Pastillas de luz</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>estado39</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Otros Equipos y Dispositivos</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>texto5</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Otros Equipos y Dispositivos</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>archivo04</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Fotos: Otros Equipos y Dispositivos</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>estado31</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>board_relation3</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Link to Fichas - Propiedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>pulse_id_mkqak00g</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ID de elemento</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>pulse_log_mkqatmxw</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Registro de creación</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>pulse_updated_mkqae7xe</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Última actualización</t>
         </is>
       </c>
     </row>
@@ -1039,7 +3126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B66"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1069,768 +3156,480 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>conectar_tableros1__1</t>
+          <t>estado_1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🌐 Propiedades</t>
+          <t>Estacionamiento</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>personas__1</t>
+          <t>texto_largo</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🌐 Solicitante</t>
+          <t>Instrucciones y ubicación: Estacionamiento</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>texto3</t>
+          <t>archivo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>📋 Descripción</t>
+          <t>Fotos: Estacionamiento</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>archivo</t>
+          <t>color</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>📋 Archivos</t>
+          <t>Rooftop / Terraza</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dup__of_estado</t>
+          <t>texto_largo7</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🌐 Prioridad</t>
+          <t>Acceso, instrucciones y horarios: Rooftop...</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>archivo5</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🌐 Estado</t>
+          <t>Fotos: Rooftop...</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>estado6__1</t>
+          <t>color0</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🌐 Equipo asignado</t>
+          <t>Gimnasio</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>personas</t>
+          <t>texto_largo2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🌐 Asignado</t>
+          <t>Instrucciones, acceso y horarios: Gimnasio</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>dup__of___asignado__1</t>
+          <t>archivo8</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🗳️ Co- Asignado</t>
+          <t>Fotos: Gimnasio</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>dup__of___link__1</t>
+          <t>dup__of_gimnasio</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🌐 PL</t>
+          <t>Alberca</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>conectar_tableros4</t>
+          <t>texto_largo0</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🌐 Reservaciones</t>
+          <t>Instrucciones, acceso y horarios: Alberca</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>personas_16</t>
+          <t>archivo0</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>📋 Notificar</t>
+          <t>Fotos: Alberca</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>creaci_n_de_registro</t>
+          <t>dup__of_alberca</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🌐 Creación</t>
+          <t>Business Center</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>bot_n8__1</t>
+          <t>texto_largo8</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>🗳️ Enviar a Mantenimiento</t>
+          <t>Instrucciones, acceso y horarios: Business Center / Sala Lounge</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>fecha1__1</t>
+          <t>archivo9</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>🗳️ Fecha Programación</t>
+          <t>Fotos: Business center / Sala Lounge</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>dup__of_prioridad__1</t>
+          <t>color4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>🌐 Categoria</t>
+          <t>Jacuzzi</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>dup__of___clasificaci_n__1</t>
+          <t>texto_largo24</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>🌐 Fuente</t>
+          <t>Instrucciones, acceso y horarios: Jacuzzi</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>reflejo4__1</t>
+          <t>archivo50</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>🌐 Payout</t>
+          <t>Fotos: Jacuzzi</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>dup__of_payout8__1</t>
+          <t>dup__of_jacuzzi</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>🌐 Precio por noche</t>
+          <t>Cine</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>dup__of_payout__1</t>
+          <t>texto_largo1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>🌐 Noches</t>
+          <t>Instrucciones, acceso y horarios: Sala de Cine</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>reflejo_1</t>
+          <t>archivo83</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>🌐 Link</t>
+          <t>Fotos: Sala de Cine</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>subelementos</t>
+          <t>dup__of_cine</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Subelementos</t>
+          <t>Juegos para niños</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>texto62</t>
+          <t>texto_largo5</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>🗳️ Descripción del trabajo realizado</t>
+          <t>Instrucciones, acceso y horarios: Juegos para niños</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>archivo4</t>
+          <t>archivo04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>🗳️ Evidencia de cierre</t>
+          <t>Fotos: Juegos para niños</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>clasificaci_n_1</t>
+          <t>color02</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Evaluación</t>
+          <t>Bodega</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>duration</t>
+          <t>texto_largo94</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>⏱️ Respuesta</t>
+          <t>Ubicación y acceso: Bodega</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>dup__of____total__1</t>
+          <t>archivo69</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>⏱️ Programación</t>
+          <t>Fotos: Bodega</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dup__of____soluci_n__1</t>
+          <t>boolean7</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>⏱️ En espera</t>
+          <t>Lavandería</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>duration__1</t>
+          <t>dup__of_bodega</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>⏱️ Resolución</t>
+          <t>Lavandería</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dup__of____en_espera__1</t>
+          <t>texto_largo4</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>⏱️ Total</t>
+          <t>Instrucciones acceso y horarios: Lavandería</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>_ltima_actualizaci_n</t>
+          <t>archivo3</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>⚙️ Última actualización</t>
+          <t>Fotos: Lavandería</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>dup__of_lavander_a</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>🌐 Fecha de cierre</t>
+          <t>Otras amenidades</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>texto__1</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>⚙️ Nombre del solicitante</t>
+          <t>Nombre</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>f_rmula__1</t>
+          <t>texto_largo9</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>🌐 Solicita</t>
+          <t>Instrucciones, acceso y horarios: Otras amenidades</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>conectar_tableros__1</t>
+          <t>archivo98</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>⚙️ Conexión para AAH en turno</t>
+          <t>Fotos: Otras amenidades</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>reflejo__1</t>
+          <t>estado</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>🌐 AAH en turno</t>
+          <t>Estado</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>dup__of_aah_en_turno__1</t>
+          <t>board_relation9</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>⚙️ AAH en turno Estado</t>
+          <t>Link to Fichas - Propiedades</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>estado__1</t>
+          <t>pulse_id_mkqaswrw</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>⚙️ AAH Reflex</t>
+          <t>ID de elemento</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>fecha__1</t>
+          <t>pulse_log_mkqamgd4</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>🌐 Fecha de realización</t>
+          <t>Registro de creación</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>f_rmula1__1</t>
+          <t>pulse_updated_mkqaj0pe</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>⚙️ Antigüedad en horas</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>formula__1</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>⚙️ Resolución en horas</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>formula7__1</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>⚙️ Programación en horas</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>formula6__1</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>⚙️ Total en horas</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>formula2__1</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>⚙️ Respuesta inicial en horas</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>f_rmula4__1</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>⚙️ Programado o Resuelto en Horas</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>texto1__1</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>🌐 Reservation Code</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>n_meros__1</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>⚙️ Tool Connect</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>dup__of____tool_connect8__1</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>⚙️ Tool Envia Manto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>dup__of____tool_connect6__1</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>⚙️ En turno</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>link_to_resoluciones__1</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>🌐 Resoluciones</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>personas2__1</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>🌐 Supervisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>reflejo6__1</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>🌐 Label Con.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>fecha12__1</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>⚙️ Timestamp Recibidos</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>hora__1</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>⚙️🕣 Timestamp Recibidos</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>hour__1</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>⚙️🕣 Timestamp Programado</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>hour2__1</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>⚙️🕣 Timestamp Realizado</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>date__1</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>⚙️ Timestamp Programado</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>date1__1</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>⚙️ Timestamp Realizado</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>date3__1</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>⚙️ Timestamp Cerrado</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>id__de_elemento__1</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>⚙️ Id. de elemento</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>conectar_tableros3__1</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>🔧 Mantenimiento</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>board_relation__1</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Control de Artículos para Huéspedes</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>board_relation9__1</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>link to Compras de Blancos</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>board_relation_mkmty0nb</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>link to 🛏️ Reservaciones</t>
+          <t>Última actualización</t>
         </is>
       </c>
     </row>
@@ -1845,7 +3644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1887,204 +3686,300 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Juegos de sábanas</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>fecha__1</t>
+          <t>archivo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fecha límite</t>
+          <t>Fotos: Juego de sábanas</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>personas__1</t>
+          <t>texto2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Responsable</t>
+          <t>Almoahadas</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>texto_largo3__1</t>
+          <t>archivo6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Comentarios de Cierre</t>
+          <t>Fotos: Almohadas</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>archivo</t>
+          <t>texto1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Evidencia de cierre</t>
+          <t>Edredones</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>archivo2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Fecha de cierre</t>
+          <t>Fotos: Edredones</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>personas1__1</t>
+          <t>texto7</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Supervisa</t>
+          <t>Fundas de edredón</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>conectar_tableros5</t>
+          <t>archivo1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Origen</t>
+          <t>Fotos: Fundas de edredón</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>texto_largo__1</t>
+          <t>texto5</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🔎 Análisis de Causa Raíz</t>
+          <t>Frazadas, cobijas o cobertores</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>long_text__1</t>
+          <t>archivo7</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>⚡️Acción correctiva</t>
+          <t>Fotos: Frazadas, cobijas o cobertores</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>estado_1__1</t>
+          <t>texto58</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Equipo</t>
+          <t>Accesorios extra camas</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>estado_17__1</t>
+          <t>archivo8</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🚦Prioridad</t>
+          <t>Fotos: Accesorios extra camas</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>fecha1__1</t>
+          <t>texto16</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Enviado a Revisión</t>
+          <t>Toallas de cuerpo completo</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>workdoc_de_monday__1</t>
+          <t>archivo27</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Acta AAH</t>
+          <t>Fotos: Toallas de cuerpo</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>estado_178__1</t>
+          <t>texto3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fuente</t>
+          <t>Toallas de mano y faciales</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>registro_de_creaci_n__1</t>
+          <t>archivo5</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>⚙️️ Creación</t>
+          <t>Fotos: Toallas de mano y faciales</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>f_rmula__1</t>
+          <t>texto8</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>⚙️ Prioridad</t>
+          <t>Tapetes de baño</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>archivo53</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Foto: Tapetes de baño</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>archivo28</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Foto de elementos de decoración importantes</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>archivo61</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Foto de cocina (Vajilla, batería, vasos, acc. para cocinar)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>estado</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>board_relation2</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>link to Fichas - Propiedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>pulse_id_mkqa46c6</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ID de elemento</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>pulse_log_mkqaft81</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Registro de creación</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>pulse_updated_mkqak8dq</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Última actualización</t>
         </is>
       </c>
     </row>
@@ -2099,7 +3994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2129,192 +4024,456 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>subelementos_mkkqhsz7</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Subelementos</t>
+          <t>Internet: Compañía</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>archivo5</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🗓️ Fecha del aviso</t>
+          <t>Internet: Foto recibo</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>texto04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚫 Penalizáción</t>
+          <t>Internet: A nombre de</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>estado_1__1</t>
+          <t>texto85</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚦Estado</t>
+          <t>Internet: Quién paga</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dup__of_fecha_del_aviso__1</t>
+          <t>texto7</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🗓️ Reactivación</t>
+          <t>Internet: Cuenta</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>texto_largo__1</t>
+          <t>archivo2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>⭐️ Evaluaciones</t>
+          <t>QR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>dup__of_evaluaciones8__1</t>
+          <t>texto9</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>✍🏻 Acciones Correctivas</t>
+          <t>Internet: Velocidad</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>bot_n__1</t>
+          <t>texto1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Apleación</t>
+          <t>Internet: Nombre WiFi</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>long_text__1</t>
+          <t>texto0</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>📨 Apelación</t>
+          <t>Internet: Contraseña</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>dup__of_apelaci_n__1</t>
+          <t>texto4</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>📩 Correo</t>
+          <t>Nombre Repetidor</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>archivo__1</t>
+          <t>texto2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>📸 Evidencias</t>
+          <t>Clave repetidor</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>conectar_tableros__1</t>
+          <t>long_text1__1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🏢 Propiedades</t>
+          <t>Fecha de pago - Internet</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>n_meros__1</t>
+          <t>texto12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Enviar tool</t>
+          <t>Netflix</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>link_to____acciones_mkkq4aj1</t>
+          <t>texto8</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>link to ⚡️ Acciones</t>
+          <t>Gas: Compañía</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>workdoc_de_monday_mkm016kp</t>
+          <t>texto5</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>🔍 Análisis Causa Raíz</t>
+          <t>Gas: No. Cuenta</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>n_meros_mkmvp9n4</t>
+          <t>texto18</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Números</t>
+          <t>Gas: Paga</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>texto27</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Gas: Método de pago</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>archivo_1__1</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Gas: Foto recibo</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>texto_mkmy84yn</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Fecha de pago gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>texto6</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CFE: No. de servicio</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>texto89</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CFE: A nombre de</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>text4</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CFE: Quién paga</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>texto817</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CFE: Estado</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>archivo</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Foto CFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>fecha_de_pago___cfe__1</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Fecha de pago - CFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>texto81</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Agua: No. de cuenta</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>texto19</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Agua: Paga</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>archivo6</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Foto Recibo Agua</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fecha_de_pago___agua__1</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Fecha de pago - Agua</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>texto__1</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Cuenta Predial</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>texto9__1</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Fecha de Pago - Predial</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>estado</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>board_relation3</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Link to Fichas - Propiedades</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>reflejo__1</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Reflejo</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>estado_1__1</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Estado 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>pulse_id_mkqaxmpc</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ID de elemento</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>pulse_log_mkqar56e</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Registro de creación</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>pulse_updated_mkqa74hg</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Última actualización</t>
         </is>
       </c>
     </row>
@@ -2329,7 +4488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2359,7 +4518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>subelementos__1</t>
+          <t>subelementos</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2371,324 +4530,180 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>conectar_tableros__1</t>
+          <t>archivo</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Reservaciones</t>
+          <t>Recámaras</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>reflejo_1__1</t>
+          <t>archivo4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Link</t>
+          <t>Sala</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>archivo6</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Check-out</t>
+          <t>Comedor</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>cobrar___1</t>
+          <t>archivo1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cobrar?</t>
+          <t>Cocina</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>texto_largo__1</t>
+          <t>archivo8</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Descripción</t>
+          <t>Baños</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>reflejo0__1</t>
+          <t>archivo5</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Evidencia</t>
+          <t>Decoración adicional</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>label__1</t>
+          <t>archivo7</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Clasificación</t>
+          <t>Elementos importantes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>fecha_1__1</t>
+          <t>archivo47</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Programación del cobro</t>
+          <t>Balcón / Terraza</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>enlace__1</t>
+          <t>archivo_mkn5as9y</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Link resolución</t>
+          <t>Amenidades</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>archivo_mkn5dvpr</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>todas las fotos</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>reflejo__1</t>
+          <t>status</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Código de Reserva</t>
+          <t>Estado - Mandar a subir el anuncio a Airbnb</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>conectar_tableros2__1</t>
+          <t>link_to_propiedades</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ticket</t>
+          <t>link to Propiedades</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>texto7__1</t>
+          <t>pulse_id_mkqaj08g</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Código de reserva</t>
+          <t>ID de elemento</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>conectar_tableros9__1</t>
+          <t>pulse_log_mkqa9355</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Propiedades</t>
+          <t>Registro de creación</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>reflejo7__1</t>
+          <t>pulse_updated_mkqa8r0v</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Reflejo</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>conectar_tableros25__1</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>☆ Evaluaciones</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>n_meros7__1</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Monto del cobro</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>f_rmula__1</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Fecha límite</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>fecha2__1</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Fecha del cobro</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>dup__of_fecha_del_cobro__1</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Fecha del seguimiento</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>archivo3__1</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Evidencias adicionales</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>texto9__1</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Código de Resolución</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>n_meros5__1</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Monto pagado</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>reflejo_17__1</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Label</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>registro_de_creaci_n_mkkdqxf2</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Registro de creación</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>_ltima_actualizaci_n_mkkvfxaz</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
           <t>Última actualización</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>archivo_mkm2973p</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Archivo</t>
         </is>
       </c>
     </row>
@@ -2703,7 +4718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B54"/>
+  <dimension ref="A1:B72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2733,24 +4748,24 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>conectar_tableros</t>
+          <t>subelementos__1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>📋 Propiedad</t>
+          <t>Subelementos</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>texto3</t>
+          <t>archivo97__1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>📋 Descripción</t>
+          <t>Fotos Check in Airbnb</t>
         </is>
       </c>
     </row>
@@ -2762,1761 +4777,811 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>📋 Archivos</t>
+          <t>Paso 1 - Foto</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>estado_1__1</t>
+          <t>texto_largo__1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>📋 Programación</t>
+          <t>Paso 1 - Español</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>fecha_1__1</t>
+          <t>long_text__1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>📋 Fecha</t>
+          <t>Paso 1 - Inglés</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>archivo__1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🔧 Fecha y hora</t>
+          <t>Paso 2 - Foto</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>texto__1</t>
+          <t>long_text2__1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>📋 Horario</t>
+          <t>Paso 2 - Español</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>personas_16</t>
+          <t>long_text0__1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>📋 Notificar a:</t>
+          <t>Paso 2 - Inglés</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>f_rmula__1</t>
+          <t>archivo3__1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🌐 Solicita</t>
+          <t>Paso 3 - Foto</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>estado_14__1</t>
+          <t>dup__of_paso_2___ingl_s__1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🌐 Prioridad</t>
+          <t>Paso 3 - Español</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>estado_11__1</t>
+          <t>long_text3__1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🌐 Estado</t>
+          <t>Paso 3 - Inglés</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>bot_n__1</t>
+          <t>archivo5__1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🔧 Recepción</t>
+          <t>Paso 4 - Foto</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>n_meros39</t>
+          <t>long_text1__1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🔧 Orden del día</t>
+          <t>Paso 4 - Español</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>lookup</t>
+          <t>dup__of_paso_3___ingl_s__1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Acceso edificio</t>
+          <t>Paso 4 - Inglés</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>reflejo41</t>
+          <t>archivo7__1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Acceso al Depto.</t>
+          <t>Paso 5 - Foto</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>dup__of___recepci_n1__1</t>
+          <t>long_text08__1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>🔧 Iniciar</t>
+          <t>Paso 5 - Español</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>dup__of___iniciar__1</t>
+          <t>long_text29__1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>🔧 Realizado</t>
+          <t>Paso 5 - Inglés</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>texto62</t>
+          <t>archivo36__1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>🔧 Descripción del trabajo realizado</t>
+          <t>Paso 6 - Foto</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>long_text</t>
+          <t>dup__of_paso_5___ingl_s__1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>🔧 Observaciones internas</t>
+          <t>Paso 6 - Español</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>archivo4</t>
+          <t>long_text7__1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>🔧 Evidencia de cierre</t>
+          <t>Paso 6 - Inglés</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>n_meros8</t>
+          <t>archivo0__1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>🔧 Costos extra</t>
+          <t>Paso 7 -Foto</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>personas</t>
+          <t>dup__of_paso_6___ingl_s__1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>🔧 Asignado</t>
+          <t>Paso 7 - Español</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>men__desplegable1</t>
+          <t>long_text8__1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>🔧 Clasificación</t>
+          <t>Paso 7 - Inglés</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>subelementos</t>
+          <t>archivo9__1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Subelementos</t>
+          <t>Paso 8 - Foto</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>hora</t>
+          <t>dup__of_paso_7___ingl_s__1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>🔧 Hora Inicio</t>
+          <t>Paso 8 - Español</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>hora9</t>
+          <t>long_text84__1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>🔧 Hora Final</t>
+          <t>Paso 8 - Inglés</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>f_rmula2</t>
+          <t>archivo91__1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>🌐 Duración</t>
+          <t>Paso 9 - Foto</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>clasificaci_n_1</t>
+          <t>texto_largo7__1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>📋 Evaluación a mantenimiento</t>
+          <t>Paso 9 - Español</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>texto_largo</t>
+          <t>long_text16__1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>📋 Comentarios de la evaluación a mantenimiento</t>
+          <t>Paso 9 - Inglés</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>conectar_tableros3</t>
+          <t>archivo77__1</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>📋 Reincidencia</t>
+          <t>Paso 10 - Foto</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>reflejo3</t>
+          <t>dup__of_paso_9___ingl_s__1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>🌐  Fecha de reincidencia</t>
+          <t>Paso 10 - Español</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>clasificaci_n_16</t>
+          <t>long_text39__1</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>🔧 Evaluación del solicitante</t>
+          <t>Paso 10 - Inglés</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>texto_largo8</t>
+          <t>archivo6__1</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>🔧 Comentarios de la evaluación al solicitante</t>
+          <t>Paso 11 - Foto</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>duration</t>
+          <t>texto_largo4__1</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>⏱️ Respuesta Inicial</t>
+          <t>Paso 11 - Español</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>duration__1</t>
+          <t>long_text9__1</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>⏱️ Programación</t>
+          <t>Paso 11 - Inglés</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>dup__of____programaci_n__1</t>
+          <t>archivo4__1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>⏱️ En Espera</t>
+          <t>Paso 12 - Foto</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>dup__of____en_espera__1</t>
+          <t>long_text6__1</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>⏱️ Total</t>
+          <t>Paso 12 - Español</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>personas_153</t>
+          <t>long_text4__1</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>⚙️ Solicita</t>
+          <t>Paso 12 - Inglés</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>creaci_n_de_registro</t>
+          <t>dup__of_paso_12___foto__1</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>⚙️ Creación</t>
+          <t>Paso 13 - Foto</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>registro_de_creaci_n__1</t>
+          <t>paso_13___espa_ol__1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>⚙️ Registro de creación</t>
+          <t>Paso 13 - Español</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>_ltima_actualizaci_n</t>
+          <t>paso_13__ingl_s__1</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>⚙️ Actualización</t>
+          <t>Paso 13- Inglès</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>estado__1</t>
+          <t>dup__of_paso_13___foto__1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>🌐 Fuente</t>
+          <t>Paso 14 - Foto</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>id__de_elemento__1</t>
+          <t>long_text48__1</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>🌐 Folio</t>
+          <t>Paso 14 - Español</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>texto9__1</t>
+          <t>dup__of_paso_13__ingl_s__1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>🌐 Código de Reserva</t>
+          <t>Paso 14- Inglès</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bot_n5__1</t>
+          <t>archivo8__1</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Enviar a Soporte</t>
+          <t>Paso 15 - Foto</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>link_to_resoluciones__1</t>
+          <t>texto_largo2__1</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>link to Resoluciones</t>
+          <t>Paso 15 - Español</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>reflejo__1</t>
+          <t>long_text88__1</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Label</t>
+          <t>Paso 15 - Inglès</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>n_meros__1</t>
+          <t>archivo82__1</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>🌐 Depto. Asigando Zap</t>
+          <t>Paso 16 - Foto</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>fecha__1</t>
+          <t>texto_largo1__1</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>⚙️ Fecha de realización</t>
+          <t>Paso 16 - Español</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>estado0__1</t>
+          <t>long_text07__1</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>📋 Tipo de Mantenimiento</t>
+          <t>Paso 16 - Inglès</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>id_de_elemento_mkm1dy3m</t>
+          <t>archivo57__1</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ID de elemento</t>
+          <t>Paso 17 - Foto</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>board_relation_mkmtvwj8</t>
+          <t>texto_largo5__1</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>link to 🛏️ Reservaciones</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B96"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Columna SQL (id)</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Columna real (title)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>subelementos</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Subelementos</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>fecha_1</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>🗓️ Fecha</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Persona</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>estado_14</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>⏰ Programación</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>bot_n6</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Supervisión</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>reflejo197</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Supervisado</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>color60</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>🚦Estado</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>estado5</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>🧳Huésped ya salió</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>archivo61</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>🧳 Foto de que no ha salido</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>texto03</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Código de Reserva</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>enlace_1__1</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>📋 Reportes</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>file8</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>🧳 Artículos olvidados</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>archivo6</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>🧾 Recibos</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>verificar78</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>✅ Revisión de artículos importantes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>verificar7</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>✅ Pisos limpios y lavados</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>boolean</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>✅ Superficies limpias y lavadas</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>boolean5</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>✅ Botes de basura con bolsa y vacíos</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>boolean0</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>✅ Cortinas abiertas (si aplica)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>boolean3</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>✅ Se regaron las plantas a las que les hace falta agua</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>boolean33</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>✅ La plancha, secadora de pelo, calentadores y ventiladores están en su lugar</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>boolean2</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>✅ Camas tendidas correctamente</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>boolean1</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>✅ No hay manchas ni pelos en sábanas, almohadas o fundas</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>boolean4</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>✅ Dos toallas por cama</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>boolean9</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>✅ Shampoo y jabón de cuerpo en la regadera</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>boolean6</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>✅ Jabón de manos en el tocador</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>boolean8</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>✅ Al menos 3 rollos de papel en el baño</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>boolean59</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>✅ Hay un tapete de baño</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>boolean94</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>✅ Hay toalla de manos en cada baño</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>boolean7</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>✅ Regadera limpia y no hay pelos en la coladera</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>boolean34</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>✅ Refrigerador y congelador vacíos y limpios</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>boolean20</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>✅ Platos y vasos limpios y guardados</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>boolean30</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>✅ Cafetera, microondas y licuadora limpios por dentro y por fuera</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>boolean79</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>✅ El filtro de agua está relleno (en caso de haber)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>boolean95</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>✅ Hay café, azúcar, aceite, sal y pimienta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>boolean85</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>✅ Mesa del comedor recogida (solo con adornos)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>boolean65</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>✅ Controles de la TV están en la mesa de centro de la sala.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>boolean29</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>✅ En caso de haber: El balcón / terraza está barrido y limpio</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>archivo__1</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>🤳🏻 Fotos de la Limpieza</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>conectar_tableros1</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>🖼️ Estándares de Presentación</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>n_meros9</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>🗓️ Noches</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>dup__of_noches</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>👥 Huéspedes</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>board_relation</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Reservaciones</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>reflejo1</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Entrada hoy</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>conectar_tableros7</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Reportes de mantenimiento por personal de limpieza</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>f_rmula5</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>🗓️ Día de la semana</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>n_meros1</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>🧺 $ Lavandería</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>dup__of_recibo2</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>🧺 Recibo Lavandería</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>label</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>🎫 Rembolsos</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>n_meros0</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>🎫 $ Reembolso</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>texto_largo7</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>🎫 Descripción reembolso</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>archivo74</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>🎫 Recibo Reembolso</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>dup__of___reembolso</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>🛏️ Pago Limpieza</t>
+          <t>Paso 17 - Español</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>dup__of_extras9</t>
+          <t>dup__of_texto_largo__1</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>🛌 Pago Ajustado Domingos</t>
+          <t>Paso 17 - Inglès</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>f_rmula0</t>
+          <t>archivo2__1</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>💰 Pago Total</t>
+          <t>Paso 18 - Foto</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>board_relation9</t>
+          <t>texto_largo9__1</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Información general</t>
+          <t>Paso 18 - Español</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>reflejo45</t>
+          <t>dup__of_texto_largo5__1</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Acceso al departamento</t>
+          <t>Paso 18 - Inglès</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>reflejo97</t>
+          <t>archivo66__1</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Acceso edificio</t>
+          <t>Paso 19 - Foto</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>reflejo839</t>
+          <t>texto_largo43__1</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Basurero</t>
+          <t>Paso 19 - Español</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>reflejo26</t>
+          <t>dup__of_texto_largo6__1</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ubicación Basurero</t>
+          <t>Paso 19 - Inglès</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>reflejo48</t>
+          <t>archivo88__1</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Instrucciones Almacén Interno</t>
+          <t>Paso 20 - Foto</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>reflejo855</t>
+          <t>texto_largo74__1</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Almacén Interno</t>
+          <t>Paso 20 - Español</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>f_rmula1</t>
+          <t>dup__of_texto_largo0__1</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Extras</t>
+          <t>Paso 20 - Inglès</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>n_meros4</t>
+          <t>n_meros__1</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Checkout ID</t>
+          <t>WIX ID</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>dup__of_checkout_id9</t>
+          <t>estado__1</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Checkout ID text</t>
+          <t>Estado</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>text__1</t>
+          <t>link_to_propiedades__1</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Checkin ID text</t>
+          <t>link to Propiedades</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>texto02</t>
+          <t>reflejo__1</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Código Reserva de reserva siguiente</t>
+          <t>Airbnb ID</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>estado_17</t>
+          <t>reflejo7__1</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Reserva siguiente encontrada</t>
+          <t>Reflejo</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>conectar_tableros__1</t>
+          <t>pulse_id_mkqa2ewa</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>☆ Evaluaciones</t>
+          <t>ID de elemento</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>reflejo_18__1</t>
+          <t>pulse_log_mkqa2a71</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Calificación Limpieza</t>
+          <t>Registro de creación</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>lookup__1</t>
+          <t>pulse_updated_mkqacfva</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Evaluación del huépsed</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>lookup8__1</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Comentarios Privados</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>lookup6__1</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Comentarios Limpieza</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>estado_15</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Revisión por coordinador</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>estado_10</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Prioridad Mantenimiento</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>bot_n7</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Enviar a mantenimiento</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>estado_1993</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Enviado a manto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>fecha_12</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Fecha mantenimiento</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>pulse_log</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Creación de registro</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>pulse_updated</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
           <t>Última actualización</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>texto6</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Motivo</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>bot_n2</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Clear propiedades</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>personas</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Proveedor</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>link_to_agenda_vero</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>link to Agenda Vero</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>board_relation26</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>hora</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Hora de inicio</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>hour</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Hora de finalización</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>f_rmula9</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Duración</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>men__desplegable5</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Zona</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>enlace__1</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Enlace</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>board_relation__1</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>link to Early check-in por asignar</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>reflejo__1</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Reflejo</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>n_meros__1</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>No. de Refresh</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>label_1__1</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>🏷️ Label</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>id_de_elemento_mkm572bd</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>ID de elemento</t>
         </is>
       </c>
     </row>
